--- a/astro-site/public/dl/haccp-templates/14-allergen-chart-reaction-protocol.xlsx
+++ b/astro-site/public/dl/haccp-templates/14-allergen-chart-reaction-protocol.xlsx
@@ -731,7 +731,7 @@
     <row r="13">
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>▸ If a reaction starts: four steps in order of urgency. The FIRST is to call 911 (UK: 999), and the second the epinephrine auto-injector if the person carries one; keeping the plate and the label comes after. You call for symptoms —trouble breathing, swelling of the lips or tongue, dizziness, vomiting, widespread hives—, not as a precaution.</t>
+          <t>▸ If a reaction starts: four steps in order of urgency. The FIRST is to give epinephrine (auto-injector) immediately if it is prescribed or available, and then call 911 (UK: 999); keeping the plate and the label comes after. You act on symptoms —trouble breathing, swelling of the lips or tongue, dizziness, vomiting, widespread hives—, not as a precaution.</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="B29" s="26" t="inlineStr">
         <is>
-          <t>Call 911 (UK: 999) for any symptom: trouble breathing, swelling of the lips or tongue, dizziness, vomiting or widespread hives. You call for SYMPTOMS, not as a precaution. It is the FIRST thing you do.</t>
+          <t>Give epinephrine (auto-injector) immediately if it is prescribed or available, and call 911 (UK: 999) for any symptom: trouble breathing, swelling of the lips or tongue, dizziness, vomiting or widespread hives. You act on SYMPTOMS, not as a precaution. It is the FIRST thing you do.</t>
         </is>
       </c>
       <c r="C29" s="27" t="n"/>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B30" s="26" t="inlineStr">
         <is>
-          <t>If the person carries an epinephrine auto-injector, help them use it following their instructions —it is given at the same time as the call. Do not move them or leave them alone.</t>
+          <t>Help the person use their own auto-injector following its instructions, and call 911 even if the symptoms ease after the epinephrine: a second reaction can follow. Do not move them or leave them alone.</t>
         </is>
       </c>
       <c r="C30" s="27" t="n"/>
